--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V5.4.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V5.4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200016\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1425035D-EDEE-4314-85B1-B4E9AC81438C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93A6A38-42D7-4673-A836-C142A05F24CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="576">
   <si>
     <t>Class</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2408,6 +2408,18 @@
 프리즘 익스플로전 설명 오류 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>드론 공격력 조정</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>강현재</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5.5</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2418,7 +2430,7 @@
     <numFmt numFmtId="177" formatCode="0.##%"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2477,6 +2489,19 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="6">
@@ -2544,7 +2569,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2724,6 +2749,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3042,18 +3073,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC70340-B386-46F7-B380-7E3B46561623}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="122.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B3" s="28">
         <v>46196</v>
       </c>
@@ -3064,7 +3095,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="323">
+    <row r="4" spans="1:4" ht="323" x14ac:dyDescent="0.45">
       <c r="B4" s="28">
         <v>46209</v>
       </c>
@@ -3075,7 +3106,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B5" s="28">
         <v>46213</v>
       </c>
@@ -3086,7 +3117,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="85">
+    <row r="6" spans="1:4" ht="85" x14ac:dyDescent="0.45">
       <c r="B6" s="28">
         <v>46218</v>
       </c>
@@ -3097,7 +3128,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>475</v>
       </c>
@@ -3111,7 +3142,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="39" t="s">
         <v>478</v>
       </c>
@@ -3125,7 +3156,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="34">
+    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>483</v>
       </c>
@@ -3139,7 +3170,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>498</v>
       </c>
@@ -3153,7 +3184,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="45" t="s">
         <v>546</v>
       </c>
@@ -3167,7 +3198,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" s="54" t="s">
         <v>561</v>
       </c>
@@ -3181,7 +3212,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>564</v>
       </c>
@@ -3195,7 +3226,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="34">
+    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A14" s="56" t="s">
         <v>569</v>
       </c>
@@ -3209,28 +3240,39 @@
         <v>476</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="B15" s="28"/>
-    </row>
-    <row r="16" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" s="62" t="s">
+        <v>575</v>
+      </c>
+      <c r="B15" s="28">
+        <v>46297</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>573</v>
+      </c>
+      <c r="D15" s="62" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B16" s="28"/>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B17" s="28"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B18" s="28"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B19" s="28"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B20" s="28"/>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B21" s="28"/>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B22" s="28"/>
     </row>
   </sheetData>
@@ -3243,7 +3285,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0AF93A4-1273-423C-B589-7C2465F14193}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
@@ -3258,12 +3300,12 @@
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B2" s="58" t="s">
         <v>211</v>
       </c>
@@ -3282,7 +3324,7 @@
       <c r="O2" s="59"/>
       <c r="P2" s="59"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="s">
         <v>176</v>
       </c>
@@ -3335,7 +3377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="s">
         <v>178</v>
       </c>
@@ -3388,7 +3430,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="34">
+    <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="s">
         <v>179</v>
       </c>
@@ -3441,7 +3483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="34">
+    <row r="7" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A7" s="7"/>
       <c r="B7" s="8">
         <v>10002</v>
@@ -3492,7 +3534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="34">
+    <row r="8" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
       <c r="B8" s="8">
         <v>10003</v>
@@ -3543,7 +3585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="34">
+    <row r="9" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
       <c r="B9" s="8">
         <v>10004</v>
@@ -3594,7 +3636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3609,7 +3651,7 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11" s="11" t="s">
         <v>180</v>
       </c>
@@ -3629,7 +3671,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="34">
+    <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>175</v>
       </c>
@@ -3682,7 +3724,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -3697,7 +3739,7 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3712,7 +3754,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3727,7 +3769,7 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3742,7 +3784,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="2:14">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3757,7 +3799,7 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="2:14">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3772,7 +3814,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="2:14">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3787,7 +3829,7 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="2:14">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -3802,7 +3844,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="2:14">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3817,7 +3859,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="2:14">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -3845,7 +3887,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BH32"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.58203125" style="11" customWidth="1"/>
@@ -3864,12 +3906,12 @@
     <col min="16" max="60" width="15.58203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B2" s="60" t="s">
         <v>211</v>
       </c>
@@ -3886,7 +3928,7 @@
       <c r="M2" s="60"/>
       <c r="N2" s="60"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>176</v>
       </c>
@@ -3915,7 +3957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>178</v>
       </c>
@@ -3944,7 +3986,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>179</v>
       </c>
@@ -3973,7 +4015,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B7" s="11">
         <v>2</v>
       </c>
@@ -3999,7 +4041,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B8" s="11">
         <v>3</v>
       </c>
@@ -4025,7 +4067,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B9" s="11">
         <v>4</v>
       </c>
@@ -4051,7 +4093,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B10" s="11">
         <v>5</v>
       </c>
@@ -4077,7 +4119,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B11" s="11">
         <v>6</v>
       </c>
@@ -4103,7 +4145,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B12" s="11">
         <v>7</v>
       </c>
@@ -4129,7 +4171,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="B13" s="11">
         <v>8</v>
       </c>
@@ -4155,12 +4197,12 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A15" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="34">
+    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.45">
       <c r="A16" s="11" t="s">
         <v>175</v>
       </c>
@@ -4189,62 +4231,62 @@
         <v>456</v>
       </c>
     </row>
-    <row r="18" spans="3:6">
+    <row r="18" spans="3:6" x14ac:dyDescent="0.45">
       <c r="E18" s="55" t="s">
         <v>566</v>
       </c>
       <c r="F18" s="12"/>
     </row>
-    <row r="19" spans="3:6">
+    <row r="19" spans="3:6" x14ac:dyDescent="0.45">
       <c r="E19" s="11" t="s">
         <v>568</v>
       </c>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="3:6">
+    <row r="20" spans="3:6" x14ac:dyDescent="0.45">
       <c r="E20" s="11" t="s">
         <v>567</v>
       </c>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="3:6">
+    <row r="21" spans="3:6" x14ac:dyDescent="0.45">
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="3:6">
+    <row r="22" spans="3:6" x14ac:dyDescent="0.45">
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="3:6">
+    <row r="23" spans="3:6" x14ac:dyDescent="0.45">
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="3:6">
+    <row r="24" spans="3:6" x14ac:dyDescent="0.45">
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="3:6">
+    <row r="25" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C25" s="19"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="3:6">
+    <row r="26" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C26" s="12"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="3:6">
+    <row r="27" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C27" s="12"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="3:6">
+    <row r="28" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="3:6">
+    <row r="29" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C29" s="12"/>
     </row>
-    <row r="30" spans="3:6">
+    <row r="30" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C30" s="12"/>
     </row>
-    <row r="31" spans="3:6">
+    <row r="31" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C31" s="12"/>
     </row>
-    <row r="32" spans="3:6">
+    <row r="32" spans="3:6" x14ac:dyDescent="0.45">
       <c r="C32" s="12"/>
     </row>
   </sheetData>
@@ -4260,7 +4302,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716AB573-FB99-421B-B82D-80DF2560487A}">
   <dimension ref="A1:AM13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.58203125" style="29" customWidth="1"/>
@@ -4289,12 +4331,12 @@
     <col min="66" max="16384" width="9" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A1" s="29" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:39">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
       <c r="B2" s="60" t="s">
         <v>215</v>
       </c>
@@ -4313,7 +4355,7 @@
       <c r="O2" s="60"/>
       <c r="P2" s="60"/>
     </row>
-    <row r="4" spans="1:39">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A4" s="29" t="s">
         <v>176</v>
       </c>
@@ -4432,7 +4474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:39">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A5" s="29" t="s">
         <v>178</v>
       </c>
@@ -4551,7 +4593,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:39" s="1" customFormat="1" ht="51">
+    <row r="6" spans="1:39" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>179</v>
       </c>
@@ -4567,8 +4609,8 @@
       <c r="E6" s="1">
         <v>5</v>
       </c>
-      <c r="F6" s="1">
-        <v>10</v>
+      <c r="F6" s="27">
+        <v>4</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -4631,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" s="1" customFormat="1" ht="102">
+    <row r="7" spans="1:39" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
         <v>427</v>
       </c>
@@ -4741,7 +4783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:39" s="1" customFormat="1" ht="68">
+    <row r="8" spans="1:39" s="1" customFormat="1" ht="68" x14ac:dyDescent="0.45">
       <c r="B8" s="1" t="s">
         <v>428</v>
       </c>
@@ -4851,7 +4893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:39" s="47" customFormat="1" ht="85">
+    <row r="9" spans="1:39" s="47" customFormat="1" ht="85" x14ac:dyDescent="0.45">
       <c r="B9" s="47" t="s">
         <v>429</v>
       </c>
@@ -4964,7 +5006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:39" s="1" customFormat="1" ht="102">
+    <row r="10" spans="1:39" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>466</v>
       </c>
@@ -4974,7 +5016,7 @@
       <c r="D10" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="1">
         <v>100</v>
       </c>
       <c r="F10" s="1">
@@ -5077,10 +5119,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:39">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
       <c r="AI11" s="35"/>
     </row>
-    <row r="12" spans="1:39" ht="136">
+    <row r="12" spans="1:39" ht="136" x14ac:dyDescent="0.45">
       <c r="A12" s="29" t="s">
         <v>180</v>
       </c>
@@ -5199,7 +5241,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="13" spans="1:39">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A13" s="29" t="s">
         <v>175</v>
       </c>
@@ -5217,7 +5259,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A705E06-4C8A-43EB-9784-7D906D56BEF6}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" style="18" customWidth="1"/>
@@ -5238,19 +5280,19 @@
     <col min="39" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" s="18" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B2" s="61" t="s">
         <v>258</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4" s="18" t="s">
         <v>176</v>
       </c>
@@ -5303,7 +5345,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5" s="18" t="s">
         <v>178</v>
       </c>
@@ -5356,7 +5398,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6" s="18" t="s">
         <v>179</v>
       </c>
@@ -5397,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B7" s="31" t="s">
         <v>523</v>
       </c>
@@ -5431,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B8" s="31" t="s">
         <v>559</v>
       </c>
@@ -5473,7 +5515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="30" customFormat="1">
+    <row r="9" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B9" s="31" t="s">
         <v>525</v>
       </c>
@@ -5515,7 +5557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="30" customFormat="1">
+    <row r="10" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B10" s="31" t="s">
         <v>526</v>
       </c>
@@ -5561,7 +5603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B11" s="31" t="s">
         <v>527</v>
       </c>
@@ -5591,7 +5633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="30" customFormat="1">
+    <row r="12" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B12" s="31" t="s">
         <v>528</v>
       </c>
@@ -5637,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="30" customFormat="1">
+    <row r="13" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B13" s="31" t="s">
         <v>529</v>
       </c>
@@ -5683,7 +5725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="30" customFormat="1">
+    <row r="14" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B14" s="31" t="s">
         <v>530</v>
       </c>
@@ -5733,7 +5775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B15" s="31" t="s">
         <v>531</v>
       </c>
@@ -5771,7 +5813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="46" customFormat="1">
+    <row r="16" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B16" s="31" t="s">
         <v>549</v>
       </c>
@@ -5801,7 +5843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="46" customFormat="1">
+    <row r="17" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B17" s="31" t="s">
         <v>550</v>
       </c>
@@ -5839,7 +5881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="46" customFormat="1">
+    <row r="18" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B18" s="31" t="s">
         <v>551</v>
       </c>
@@ -5877,7 +5919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="46" customFormat="1">
+    <row r="19" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B19" s="31" t="s">
         <v>548</v>
       </c>
@@ -5915,12 +5957,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="C20" s="32"/>
       <c r="P20" s="32"/>
       <c r="Q20" s="32"/>
     </row>
-    <row r="21" spans="1:17">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21" s="18" t="s">
         <v>180</v>
       </c>
@@ -5973,12 +6015,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="22" spans="1:17">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22" s="18" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:17">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B23" s="1" t="s">
         <v>426</v>
       </c>
@@ -5996,7 +6038,7 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" spans="1:17">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B24" s="1" t="s">
         <v>427</v>
       </c>
@@ -6014,7 +6056,7 @@
       <c r="H24" s="42"/>
       <c r="I24" s="42"/>
     </row>
-    <row r="25" spans="1:17">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B25" s="1" t="s">
         <v>428</v>
       </c>
@@ -6032,7 +6074,7 @@
       <c r="H25" s="42"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" spans="1:17">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B26" s="47" t="s">
         <v>429</v>
       </c>
@@ -6046,7 +6088,7 @@
       <c r="H26" s="42"/>
       <c r="I26" s="42"/>
     </row>
-    <row r="27" spans="1:17">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B27" s="1" t="s">
         <v>466</v>
       </c>
@@ -6060,7 +6102,7 @@
       <c r="H27" s="30"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" spans="1:17">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
@@ -6068,7 +6110,7 @@
       <c r="H28" s="30"/>
       <c r="I28" s="30"/>
     </row>
-    <row r="29" spans="1:17">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
       <c r="B29" s="42" t="s">
         <v>520</v>
       </c>
@@ -6090,7 +6132,7 @@
       </c>
       <c r="I29" s="30"/>
     </row>
-    <row r="30" spans="1:17" s="42" customFormat="1">
+    <row r="30" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C30" s="53" t="s">
         <v>544</v>
       </c>
@@ -6104,7 +6146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="42" customFormat="1">
+    <row r="31" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C31" s="21">
         <v>3</v>
       </c>
@@ -6118,8 +6160,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="42" customFormat="1"/>
-    <row r="33" spans="2:9">
+    <row r="32" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B33" s="42" t="s">
         <v>522</v>
       </c>
@@ -6141,7 +6183,7 @@
       </c>
       <c r="I33" s="30"/>
     </row>
-    <row r="34" spans="2:9" s="42" customFormat="1">
+    <row r="34" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C34" s="53" t="s">
         <v>544</v>
       </c>
@@ -6155,7 +6197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:9" s="42" customFormat="1">
+    <row r="35" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C35" s="21">
         <v>3</v>
       </c>
@@ -6169,8 +6211,8 @@
         <v>542</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="42" customFormat="1"/>
-    <row r="37" spans="2:9">
+    <row r="36" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B37" s="42" t="s">
         <v>524</v>
       </c>
@@ -6192,7 +6234,7 @@
       </c>
       <c r="I37" s="30"/>
     </row>
-    <row r="38" spans="2:9" s="42" customFormat="1">
+    <row r="38" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C38" s="53" t="s">
         <v>544</v>
       </c>
@@ -6206,7 +6248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="42" customFormat="1">
+    <row r="39" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C39" s="53" t="s">
         <v>544</v>
       </c>
@@ -6220,8 +6262,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="42" customFormat="1"/>
-    <row r="41" spans="2:9">
+    <row r="40" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B41" s="42" t="s">
         <v>525</v>
       </c>
@@ -6243,7 +6285,7 @@
       </c>
       <c r="I41" s="30"/>
     </row>
-    <row r="42" spans="2:9" s="42" customFormat="1">
+    <row r="42" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C42" s="21">
         <v>2</v>
       </c>
@@ -6257,7 +6299,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="42" customFormat="1">
+    <row r="43" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C43" s="53" t="s">
         <v>544</v>
       </c>
@@ -6271,8 +6313,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="42" customFormat="1"/>
-    <row r="45" spans="2:9">
+    <row r="44" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B45" s="42" t="s">
         <v>526</v>
       </c>
@@ -6294,7 +6336,7 @@
       </c>
       <c r="I45" s="30"/>
     </row>
-    <row r="46" spans="2:9" s="42" customFormat="1">
+    <row r="46" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C46" s="53" t="s">
         <v>544</v>
       </c>
@@ -6308,7 +6350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="42" customFormat="1">
+    <row r="47" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C47" s="53" t="s">
         <v>560</v>
       </c>
@@ -6322,8 +6364,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="42" customFormat="1"/>
-    <row r="49" spans="4:9">
+    <row r="48" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
+    <row r="49" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D49" s="30"/>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -6331,7 +6373,7 @@
       <c r="H49" s="30"/>
       <c r="I49" s="30"/>
     </row>
-    <row r="50" spans="4:9">
+    <row r="50" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D50" s="30"/>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -6339,7 +6381,7 @@
       <c r="H50" s="30"/>
       <c r="I50" s="30"/>
     </row>
-    <row r="51" spans="4:9">
+    <row r="51" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D51" s="30"/>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -6347,7 +6389,7 @@
       <c r="H51" s="30"/>
       <c r="I51" s="30"/>
     </row>
-    <row r="52" spans="4:9">
+    <row r="52" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D52" s="30"/>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -6355,7 +6397,7 @@
       <c r="H52" s="30"/>
       <c r="I52" s="30"/>
     </row>
-    <row r="53" spans="4:9">
+    <row r="53" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -6363,14 +6405,14 @@
       <c r="H53" s="30"/>
       <c r="I53" s="30"/>
     </row>
-    <row r="54" spans="4:9">
+    <row r="54" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
       <c r="G54" s="30"/>
       <c r="I54" s="30"/>
     </row>
-    <row r="55" spans="4:9">
+    <row r="55" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -6378,7 +6420,7 @@
       <c r="H55" s="30"/>
       <c r="I55" s="30"/>
     </row>
-    <row r="56" spans="4:9">
+    <row r="56" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
       <c r="F56" s="30"/>
@@ -6386,7 +6428,7 @@
       <c r="H56" s="30"/>
       <c r="I56" s="30"/>
     </row>
-    <row r="57" spans="4:9">
+    <row r="57" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D57" s="30"/>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
@@ -6394,7 +6436,7 @@
       <c r="H57" s="30"/>
       <c r="I57" s="30"/>
     </row>
-    <row r="58" spans="4:9">
+    <row r="58" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D58" s="30"/>
       <c r="E58" s="30"/>
       <c r="F58" s="30"/>
@@ -6402,7 +6444,7 @@
       <c r="H58" s="30"/>
       <c r="I58" s="30"/>
     </row>
-    <row r="59" spans="4:9">
+    <row r="59" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D59" s="30"/>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
@@ -6410,7 +6452,7 @@
       <c r="H59" s="30"/>
       <c r="I59" s="30"/>
     </row>
-    <row r="60" spans="4:9">
+    <row r="60" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D60" s="30"/>
       <c r="E60" s="30"/>
       <c r="F60" s="30"/>
@@ -6418,7 +6460,7 @@
       <c r="H60" s="30"/>
       <c r="I60" s="30"/>
     </row>
-    <row r="61" spans="4:9">
+    <row r="61" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D61" s="30"/>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
@@ -6426,7 +6468,7 @@
       <c r="H61" s="30"/>
       <c r="I61" s="30"/>
     </row>
-    <row r="62" spans="4:9">
+    <row r="62" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D62" s="30"/>
       <c r="E62" s="30"/>
       <c r="F62" s="30"/>
@@ -6434,7 +6476,7 @@
       <c r="H62" s="30"/>
       <c r="I62" s="30"/>
     </row>
-    <row r="63" spans="4:9">
+    <row r="63" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D63" s="30"/>
       <c r="E63" s="30"/>
       <c r="F63" s="30"/>
@@ -6442,7 +6484,7 @@
       <c r="H63" s="30"/>
       <c r="I63" s="30"/>
     </row>
-    <row r="64" spans="4:9">
+    <row r="64" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D64" s="30"/>
       <c r="E64" s="30"/>
       <c r="F64" s="30"/>
@@ -6450,7 +6492,7 @@
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
     </row>
-    <row r="65" spans="4:9">
+    <row r="65" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D65" s="30"/>
       <c r="E65" s="30"/>
       <c r="F65" s="30"/>
@@ -6458,7 +6500,7 @@
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
     </row>
-    <row r="66" spans="4:9">
+    <row r="66" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D66" s="30"/>
       <c r="E66" s="30"/>
       <c r="F66" s="30"/>
@@ -6466,7 +6508,7 @@
       <c r="H66" s="30"/>
       <c r="I66" s="30"/>
     </row>
-    <row r="67" spans="4:9">
+    <row r="67" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D67" s="30"/>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
@@ -6474,7 +6516,7 @@
       <c r="H67" s="30"/>
       <c r="I67" s="30"/>
     </row>
-    <row r="68" spans="4:9">
+    <row r="68" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D68" s="30"/>
       <c r="E68" s="30"/>
       <c r="F68" s="30"/>
@@ -6482,7 +6524,7 @@
       <c r="H68" s="30"/>
       <c r="I68" s="30"/>
     </row>
-    <row r="69" spans="4:9">
+    <row r="69" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D69" s="30"/>
       <c r="E69" s="30"/>
       <c r="F69" s="30"/>
@@ -6490,7 +6532,7 @@
       <c r="H69" s="30"/>
       <c r="I69" s="30"/>
     </row>
-    <row r="70" spans="4:9">
+    <row r="70" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D70" s="30"/>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
@@ -6498,7 +6540,7 @@
       <c r="H70" s="30"/>
       <c r="I70" s="30"/>
     </row>
-    <row r="71" spans="4:9">
+    <row r="71" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D71" s="30"/>
       <c r="E71" s="30"/>
       <c r="F71" s="30"/>
@@ -6506,7 +6548,7 @@
       <c r="H71" s="30"/>
       <c r="I71" s="30"/>
     </row>
-    <row r="72" spans="4:9">
+    <row r="72" spans="4:9" x14ac:dyDescent="0.45">
       <c r="D72" s="30"/>
       <c r="E72" s="30"/>
       <c r="F72" s="30"/>
@@ -6527,7 +6569,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEBB537-D2E1-4D20-A494-C05A81D52093}">
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
@@ -6548,12 +6590,12 @@
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
       <c r="B2" s="58" t="s">
         <v>217</v>
       </c>
@@ -6572,7 +6614,7 @@
       <c r="O2" s="59"/>
       <c r="P2" s="59"/>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A4" s="57" t="s">
         <v>176</v>
       </c>
@@ -6652,7 +6694,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A5" s="57" t="s">
         <v>178</v>
       </c>
@@ -6732,7 +6774,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A6" s="57" t="s">
         <v>179</v>
       </c>
@@ -6798,7 +6840,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="23" customFormat="1">
+    <row r="7" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="57"/>
       <c r="B7" s="1" t="s">
         <v>318</v>
@@ -6880,7 +6922,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="23" customFormat="1">
+    <row r="8" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A8" s="57"/>
       <c r="B8" s="1" t="s">
         <v>319</v>
@@ -6964,7 +7006,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="23" customFormat="1">
+    <row r="9" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="57"/>
       <c r="B9" s="1" t="s">
         <v>320</v>
@@ -7028,7 +7070,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="23" customFormat="1">
+    <row r="10" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A10" s="57"/>
       <c r="B10" s="1" t="s">
         <v>322</v>
@@ -7094,7 +7136,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="23" customFormat="1">
+    <row r="11" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A11" s="57"/>
       <c r="B11" s="1" t="s">
         <v>324</v>
@@ -7178,7 +7220,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="23" customFormat="1">
+    <row r="12" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A12" s="57"/>
       <c r="B12" s="1" t="s">
         <v>326</v>
@@ -7264,7 +7306,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="23" customFormat="1">
+    <row r="13" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A13" s="57"/>
       <c r="B13" s="1" t="s">
         <v>328</v>
@@ -7330,7 +7372,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="23" customFormat="1">
+    <row r="14" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="57"/>
       <c r="B14" s="1" t="s">
         <v>344</v>
@@ -7394,7 +7436,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="23" customFormat="1">
+    <row r="15" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="57"/>
       <c r="B15" s="1" t="s">
         <v>345</v>
@@ -7478,7 +7520,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="23" customFormat="1">
+    <row r="16" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="57"/>
       <c r="B16" s="1" t="s">
         <v>346</v>
@@ -7546,7 +7588,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="23" customFormat="1">
+    <row r="17" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="57"/>
       <c r="B17" s="1" t="s">
         <v>347</v>
@@ -7624,7 +7666,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="23" customFormat="1">
+    <row r="18" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="57"/>
       <c r="B18" s="1" t="s">
         <v>348</v>
@@ -7690,7 +7732,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="23" customFormat="1">
+    <row r="19" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="57"/>
       <c r="B19" s="1" t="s">
         <v>349</v>
@@ -7776,7 +7818,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="20" spans="1:26" s="23" customFormat="1">
+    <row r="20" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="57"/>
       <c r="B20" s="1" t="s">
         <v>351</v>
@@ -7844,7 +7886,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="23" customFormat="1">
+    <row r="21" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="57"/>
       <c r="B21" s="1" t="s">
         <v>353</v>
@@ -7924,7 +7966,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="23" customFormat="1">
+    <row r="22" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A22" s="57"/>
       <c r="B22" s="1" t="s">
         <v>367</v>
@@ -7988,7 +8030,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="23" spans="1:26" s="23" customFormat="1">
+    <row r="23" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A23" s="57"/>
       <c r="B23" s="1" t="s">
         <v>369</v>
@@ -8066,7 +8108,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="24" spans="1:26" s="23" customFormat="1">
+    <row r="24" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A24" s="57"/>
       <c r="B24" s="1" t="s">
         <v>371</v>
@@ -8148,7 +8190,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:26" s="23" customFormat="1">
+    <row r="25" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A25" s="57"/>
       <c r="B25" s="1" t="s">
         <v>373</v>
@@ -8226,7 +8268,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="23" customFormat="1">
+    <row r="26" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A26" s="57"/>
       <c r="B26" s="1" t="s">
         <v>375</v>
@@ -8292,7 +8334,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="23" customFormat="1">
+    <row r="27" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A27" s="57"/>
       <c r="B27" s="1" t="s">
         <v>377</v>
@@ -8372,7 +8414,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="23" customFormat="1">
+    <row r="28" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A28" s="57"/>
       <c r="B28" s="1" t="s">
         <v>379</v>
@@ -8456,7 +8498,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="23" customFormat="1">
+    <row r="29" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A29" s="57"/>
       <c r="B29" s="1" t="s">
         <v>381</v>
@@ -8536,7 +8578,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="30" spans="1:26" s="23" customFormat="1">
+    <row r="30" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="57"/>
       <c r="B30" s="1" t="s">
         <v>395</v>
@@ -8600,7 +8642,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:26" s="23" customFormat="1">
+    <row r="31" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A31" s="57"/>
       <c r="B31" s="1" t="s">
         <v>397</v>
@@ -8664,7 +8706,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:26" s="23" customFormat="1">
+    <row r="32" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A32" s="57"/>
       <c r="B32" s="1" t="s">
         <v>399</v>
@@ -8748,7 +8790,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" spans="1:26" s="23" customFormat="1" ht="34">
+    <row r="33" spans="1:26" s="23" customFormat="1" ht="34" x14ac:dyDescent="0.45">
       <c r="A33" s="57"/>
       <c r="B33" s="1" t="s">
         <v>401</v>
@@ -8826,7 +8868,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="34" spans="1:26" s="23" customFormat="1">
+    <row r="34" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A34" s="57"/>
       <c r="B34" s="1" t="s">
         <v>403</v>
@@ -8892,7 +8934,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:26" s="23" customFormat="1">
+    <row r="35" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A35" s="57"/>
       <c r="B35" s="1" t="s">
         <v>405</v>
@@ -8958,7 +9000,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:26" s="23" customFormat="1">
+    <row r="36" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A36" s="57"/>
       <c r="B36" s="1" t="s">
         <v>407</v>
@@ -9044,7 +9086,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="37" spans="1:26" s="23" customFormat="1">
+    <row r="37" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A37" s="57"/>
       <c r="B37" s="1" t="s">
         <v>409</v>
@@ -9124,7 +9166,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="39" spans="1:26">
+    <row r="39" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A39" s="11" t="s">
         <v>180</v>
       </c>
@@ -9204,7 +9246,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="40" spans="1:26">
+    <row r="40" spans="1:26" x14ac:dyDescent="0.45">
       <c r="A40" s="11" t="s">
         <v>175</v>
       </c>
@@ -9222,7 +9264,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047AFDEF-8474-49A1-AB6C-5E66602F6994}">
   <dimension ref="A1:AR13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" customWidth="1"/>
     <col min="2" max="3" width="20.58203125" style="11" customWidth="1"/>
@@ -9249,12 +9291,12 @@
     <col min="45" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:44">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B2" s="58" t="s">
         <v>210</v>
       </c>
@@ -9278,7 +9320,7 @@
       <c r="T2" s="59"/>
       <c r="U2" s="59"/>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>176</v>
       </c>
@@ -9349,7 +9391,7 @@
         <v>18</v>
       </c>
       <c r="X4" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y4" s="10" t="s">
         <v>19</v>
@@ -9412,7 +9454,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="34">
+    <row r="5" spans="1:44" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="11" t="s">
         <v>178</v>
       </c>
@@ -9546,7 +9588,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="51">
+    <row r="6" spans="1:44" ht="51" x14ac:dyDescent="0.45">
       <c r="A6" s="11" t="s">
         <v>179</v>
       </c>
@@ -9648,7 +9690,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="34">
+    <row r="7" spans="1:44" ht="34" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>294</v>
       </c>
@@ -9747,7 +9789,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="51">
+    <row r="8" spans="1:44" ht="51" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
         <v>295</v>
       </c>
@@ -9846,7 +9888,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="34">
+    <row r="9" spans="1:44" ht="34" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>296</v>
       </c>
@@ -9945,7 +9987,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="34">
+    <row r="10" spans="1:44" ht="34" x14ac:dyDescent="0.45">
       <c r="B10" s="13" t="s">
         <v>297</v>
       </c>
@@ -10044,12 +10086,12 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:44">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.45">
       <c r="A12" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="102">
+    <row r="13" spans="1:44" ht="102" x14ac:dyDescent="0.45">
       <c r="A13" s="11" t="s">
         <v>175</v>
       </c>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V5.4.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 알파 전투 밸런스 데이터 테이블 V5.4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200016\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HeroInfluencetmp\Assets\_ProtoType_Merge\ASB\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93A6A38-42D7-4673-A836-C142A05F24CE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9742C1-00E4-49AE-B3DE-6C8F4CED8077}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -2430,7 +2430,7 @@
     <numFmt numFmtId="177" formatCode="0.##%"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2738,6 +2738,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2749,12 +2755,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3073,18 +3073,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC70340-B386-46F7-B380-7E3B46561623}">
   <dimension ref="A2:D22"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="122.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="C2" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="B3" s="28">
         <v>46196</v>
       </c>
@@ -3095,7 +3095,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="323" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="323">
       <c r="B4" s="28">
         <v>46209</v>
       </c>
@@ -3106,7 +3106,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="B5" s="28">
         <v>46213</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="85" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="85">
       <c r="B6" s="28">
         <v>46218</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>475</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" s="39" t="s">
         <v>478</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="34">
       <c r="A9" t="s">
         <v>483</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>498</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4">
       <c r="A11" s="45" t="s">
         <v>546</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4">
       <c r="A12" s="54" t="s">
         <v>561</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>564</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" ht="34">
       <c r="A14" s="56" t="s">
         <v>569</v>
       </c>
@@ -3240,39 +3240,39 @@
         <v>476</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A15" s="62" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="58" t="s">
         <v>575</v>
       </c>
       <c r="B15" s="28">
         <v>46297</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C15" s="59" t="s">
         <v>573</v>
       </c>
-      <c r="D15" s="62" t="s">
+      <c r="D15" s="58" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4">
       <c r="B16" s="28"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:2">
       <c r="B17" s="28"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:2">
       <c r="B18" s="28"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:2">
       <c r="B19" s="28"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:2">
       <c r="B20" s="28"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:2">
       <c r="B21" s="28"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:2">
       <c r="B22" s="28"/>
     </row>
   </sheetData>
@@ -3285,7 +3285,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0AF93A4-1273-423C-B589-7C2465F14193}">
   <dimension ref="A1:Q22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
@@ -3300,31 +3300,31 @@
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="58" t="s">
+    <row r="2" spans="1:17">
+      <c r="B2" s="60" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="7" t="s">
         <v>176</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17">
       <c r="A5" s="7" t="s">
         <v>178</v>
       </c>
@@ -3430,7 +3430,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="34" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17" ht="34">
       <c r="A6" s="7" t="s">
         <v>179</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="34" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17" ht="34">
       <c r="A7" s="7"/>
       <c r="B7" s="8">
         <v>10002</v>
@@ -3534,7 +3534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="34" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17" ht="34">
       <c r="A8" s="7"/>
       <c r="B8" s="8">
         <v>10003</v>
@@ -3585,7 +3585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" ht="34">
       <c r="A9" s="7"/>
       <c r="B9" s="8">
         <v>10004</v>
@@ -3636,7 +3636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -3651,7 +3651,7 @@
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17">
       <c r="A11" s="11" t="s">
         <v>180</v>
       </c>
@@ -3671,7 +3671,7 @@
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:17" ht="34" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" ht="34">
       <c r="A12" s="11" t="s">
         <v>175</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -3739,7 +3739,7 @@
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -3754,7 +3754,7 @@
       <c r="M14" s="1"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -3769,7 +3769,7 @@
       <c r="M15" s="1"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -3784,7 +3784,7 @@
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:14">
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3799,7 +3799,7 @@
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:14">
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -3814,7 +3814,7 @@
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:14">
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3829,7 +3829,7 @@
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:14">
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -3844,7 +3844,7 @@
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:14">
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3859,7 +3859,7 @@
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:14">
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -3887,7 +3887,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BH32"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.58203125" style="11" customWidth="1"/>
@@ -3906,29 +3906,29 @@
     <col min="16" max="60" width="15.58203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="B2" s="60" t="s">
+    <row r="2" spans="1:14">
+      <c r="B2" s="62" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="11" t="s">
         <v>176</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:14">
       <c r="A5" s="11" t="s">
         <v>178</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14">
       <c r="A6" s="11" t="s">
         <v>179</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14">
       <c r="B7" s="11">
         <v>2</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14">
       <c r="B8" s="11">
         <v>3</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14">
       <c r="B9" s="11">
         <v>4</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:14">
       <c r="B10" s="11">
         <v>5</v>
       </c>
@@ -4119,7 +4119,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:14">
       <c r="B11" s="11">
         <v>6</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:14">
       <c r="B12" s="11">
         <v>7</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14">
       <c r="B13" s="11">
         <v>8</v>
       </c>
@@ -4197,12 +4197,12 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:14">
       <c r="A15" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="34" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:14" ht="34">
       <c r="A16" s="11" t="s">
         <v>175</v>
       </c>
@@ -4231,62 +4231,62 @@
         <v>456</v>
       </c>
     </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6">
       <c r="E18" s="55" t="s">
         <v>566</v>
       </c>
       <c r="F18" s="12"/>
     </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6">
       <c r="E19" s="11" t="s">
         <v>568</v>
       </c>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6">
       <c r="E20" s="11" t="s">
         <v>567</v>
       </c>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6">
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6">
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6">
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6">
       <c r="F24" s="12"/>
     </row>
-    <row r="25" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6">
       <c r="C25" s="19"/>
       <c r="F25" s="12"/>
     </row>
-    <row r="26" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6">
       <c r="C26" s="12"/>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6">
       <c r="C27" s="12"/>
       <c r="F27" s="12"/>
     </row>
-    <row r="28" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6">
       <c r="C28" s="12"/>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6">
       <c r="C29" s="12"/>
     </row>
-    <row r="30" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6">
       <c r="C30" s="12"/>
     </row>
-    <row r="31" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6">
       <c r="C31" s="12"/>
     </row>
-    <row r="32" spans="3:6" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6">
       <c r="C32" s="12"/>
     </row>
   </sheetData>
@@ -4302,7 +4302,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716AB573-FB99-421B-B82D-80DF2560487A}">
   <dimension ref="A1:AM13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="29" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="15.58203125" style="29" customWidth="1"/>
@@ -4331,31 +4331,31 @@
     <col min="66" max="16384" width="9" style="29"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:39">
       <c r="A1" s="29" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
-      <c r="B2" s="60" t="s">
+    <row r="2" spans="1:39">
+      <c r="B2" s="62" t="s">
         <v>215</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
-      <c r="J2" s="60"/>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="62"/>
+      <c r="M2" s="62"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="62"/>
+    </row>
+    <row r="4" spans="1:39">
       <c r="A4" s="29" t="s">
         <v>176</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:39">
       <c r="A5" s="29" t="s">
         <v>178</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="6" spans="1:39" s="1" customFormat="1" ht="51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:39" s="1" customFormat="1" ht="51">
       <c r="A6" s="1" t="s">
         <v>179</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:39" s="1" customFormat="1" ht="102">
       <c r="B7" s="1" t="s">
         <v>427</v>
       </c>
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:39" s="1" customFormat="1" ht="68" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:39" s="1" customFormat="1" ht="68">
       <c r="B8" s="1" t="s">
         <v>428</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:39" s="47" customFormat="1" ht="85" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:39" s="47" customFormat="1" ht="85">
       <c r="B9" s="47" t="s">
         <v>429</v>
       </c>
@@ -5006,7 +5006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:39" s="1" customFormat="1" ht="102" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:39" s="1" customFormat="1" ht="102">
       <c r="B10" s="1" t="s">
         <v>466</v>
       </c>
@@ -5119,10 +5119,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:39">
       <c r="AI11" s="35"/>
     </row>
-    <row r="12" spans="1:39" ht="136" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:39" ht="136">
       <c r="A12" s="29" t="s">
         <v>180</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:39">
       <c r="A13" s="29" t="s">
         <v>175</v>
       </c>
@@ -5259,7 +5259,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A705E06-4C8A-43EB-9784-7D906D56BEF6}">
   <dimension ref="A1:Q72"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.58203125" style="18" customWidth="1"/>
@@ -5280,19 +5280,19 @@
     <col min="39" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17">
       <c r="A1" s="18" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="B2" s="61" t="s">
+    <row r="2" spans="1:17">
+      <c r="B2" s="63" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" s="18" t="s">
         <v>176</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:17">
       <c r="A5" s="18" t="s">
         <v>178</v>
       </c>
@@ -5398,7 +5398,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:17">
       <c r="A6" s="18" t="s">
         <v>179</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:17">
       <c r="B7" s="31" t="s">
         <v>523</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:17">
       <c r="B8" s="31" t="s">
         <v>559</v>
       </c>
@@ -5515,7 +5515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:17" s="30" customFormat="1">
       <c r="B9" s="31" t="s">
         <v>525</v>
       </c>
@@ -5557,7 +5557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:17" s="30" customFormat="1">
       <c r="B10" s="31" t="s">
         <v>526</v>
       </c>
@@ -5603,7 +5603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:17">
       <c r="B11" s="31" t="s">
         <v>527</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:17" s="30" customFormat="1">
       <c r="B12" s="31" t="s">
         <v>528</v>
       </c>
@@ -5679,7 +5679,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:17" s="30" customFormat="1">
       <c r="B13" s="31" t="s">
         <v>529</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="30" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:17" s="30" customFormat="1">
       <c r="B14" s="31" t="s">
         <v>530</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17">
       <c r="B15" s="31" t="s">
         <v>531</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" s="46" customFormat="1">
       <c r="B16" s="31" t="s">
         <v>549</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:17" s="46" customFormat="1">
       <c r="B17" s="31" t="s">
         <v>550</v>
       </c>
@@ -5881,7 +5881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:17" s="46" customFormat="1">
       <c r="B18" s="31" t="s">
         <v>551</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="46" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:17" s="46" customFormat="1">
       <c r="B19" s="31" t="s">
         <v>548</v>
       </c>
@@ -5957,12 +5957,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:17">
       <c r="C20" s="32"/>
       <c r="P20" s="32"/>
       <c r="Q20" s="32"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:17">
       <c r="A21" s="18" t="s">
         <v>180</v>
       </c>
@@ -6015,12 +6015,12 @@
         <v>279</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:17">
       <c r="A22" s="18" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:17">
       <c r="B23" s="1" t="s">
         <v>426</v>
       </c>
@@ -6038,7 +6038,7 @@
       <c r="H23" s="42"/>
       <c r="I23" s="42"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:17">
       <c r="B24" s="1" t="s">
         <v>427</v>
       </c>
@@ -6056,7 +6056,7 @@
       <c r="H24" s="42"/>
       <c r="I24" s="42"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:17">
       <c r="B25" s="1" t="s">
         <v>428</v>
       </c>
@@ -6074,7 +6074,7 @@
       <c r="H25" s="42"/>
       <c r="I25" s="42"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:17">
       <c r="B26" s="47" t="s">
         <v>429</v>
       </c>
@@ -6088,7 +6088,7 @@
       <c r="H26" s="42"/>
       <c r="I26" s="42"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:17">
       <c r="B27" s="1" t="s">
         <v>466</v>
       </c>
@@ -6102,7 +6102,7 @@
       <c r="H27" s="30"/>
       <c r="I27" s="42"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:17">
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
       <c r="F28" s="30"/>
@@ -6110,7 +6110,7 @@
       <c r="H28" s="30"/>
       <c r="I28" s="30"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:17">
       <c r="B29" s="42" t="s">
         <v>520</v>
       </c>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I29" s="30"/>
     </row>
-    <row r="30" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:17" s="42" customFormat="1">
       <c r="C30" s="53" t="s">
         <v>544</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:17" s="42" customFormat="1">
       <c r="C31" s="21">
         <v>3</v>
       </c>
@@ -6160,8 +6160,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:17" s="42" customFormat="1"/>
+    <row r="33" spans="2:9">
       <c r="B33" s="42" t="s">
         <v>522</v>
       </c>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="I33" s="30"/>
     </row>
-    <row r="34" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:9" s="42" customFormat="1">
       <c r="C34" s="53" t="s">
         <v>544</v>
       </c>
@@ -6197,7 +6197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:9" s="42" customFormat="1">
       <c r="C35" s="21">
         <v>3</v>
       </c>
@@ -6211,8 +6211,8 @@
         <v>542</v>
       </c>
     </row>
-    <row r="36" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:9" s="42" customFormat="1"/>
+    <row r="37" spans="2:9">
       <c r="B37" s="42" t="s">
         <v>524</v>
       </c>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="I37" s="30"/>
     </row>
-    <row r="38" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:9" s="42" customFormat="1">
       <c r="C38" s="53" t="s">
         <v>544</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:9" s="42" customFormat="1">
       <c r="C39" s="53" t="s">
         <v>544</v>
       </c>
@@ -6262,8 +6262,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="40" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:9" s="42" customFormat="1"/>
+    <row r="41" spans="2:9">
       <c r="B41" s="42" t="s">
         <v>525</v>
       </c>
@@ -6285,7 +6285,7 @@
       </c>
       <c r="I41" s="30"/>
     </row>
-    <row r="42" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:9" s="42" customFormat="1">
       <c r="C42" s="21">
         <v>2</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="43" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:9" s="42" customFormat="1">
       <c r="C43" s="53" t="s">
         <v>544</v>
       </c>
@@ -6313,8 +6313,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="44" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:9" s="42" customFormat="1"/>
+    <row r="45" spans="2:9">
       <c r="B45" s="42" t="s">
         <v>526</v>
       </c>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I45" s="30"/>
     </row>
-    <row r="46" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:9" s="42" customFormat="1">
       <c r="C46" s="53" t="s">
         <v>544</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:9" s="42" customFormat="1">
       <c r="C47" s="53" t="s">
         <v>560</v>
       </c>
@@ -6364,8 +6364,8 @@
         <v>543</v>
       </c>
     </row>
-    <row r="48" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:9" s="42" customFormat="1"/>
+    <row r="49" spans="4:9">
       <c r="D49" s="30"/>
       <c r="E49" s="30"/>
       <c r="F49" s="30"/>
@@ -6373,7 +6373,7 @@
       <c r="H49" s="30"/>
       <c r="I49" s="30"/>
     </row>
-    <row r="50" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="4:9">
       <c r="D50" s="30"/>
       <c r="E50" s="30"/>
       <c r="F50" s="30"/>
@@ -6381,7 +6381,7 @@
       <c r="H50" s="30"/>
       <c r="I50" s="30"/>
     </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="4:9">
       <c r="D51" s="30"/>
       <c r="E51" s="30"/>
       <c r="F51" s="30"/>
@@ -6389,7 +6389,7 @@
       <c r="H51" s="30"/>
       <c r="I51" s="30"/>
     </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="4:9">
       <c r="D52" s="30"/>
       <c r="E52" s="30"/>
       <c r="F52" s="30"/>
@@ -6397,7 +6397,7 @@
       <c r="H52" s="30"/>
       <c r="I52" s="30"/>
     </row>
-    <row r="53" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="4:9">
       <c r="D53" s="30"/>
       <c r="E53" s="30"/>
       <c r="F53" s="30"/>
@@ -6405,14 +6405,14 @@
       <c r="H53" s="30"/>
       <c r="I53" s="30"/>
     </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="4:9">
       <c r="D54" s="30"/>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
       <c r="G54" s="30"/>
       <c r="I54" s="30"/>
     </row>
-    <row r="55" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="4:9">
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
@@ -6420,7 +6420,7 @@
       <c r="H55" s="30"/>
       <c r="I55" s="30"/>
     </row>
-    <row r="56" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="4:9">
       <c r="D56" s="30"/>
       <c r="E56" s="30"/>
       <c r="F56" s="30"/>
@@ -6428,7 +6428,7 @@
       <c r="H56" s="30"/>
       <c r="I56" s="30"/>
     </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="4:9">
       <c r="D57" s="30"/>
       <c r="E57" s="30"/>
       <c r="F57" s="30"/>
@@ -6436,7 +6436,7 @@
       <c r="H57" s="30"/>
       <c r="I57" s="30"/>
     </row>
-    <row r="58" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="4:9">
       <c r="D58" s="30"/>
       <c r="E58" s="30"/>
       <c r="F58" s="30"/>
@@ -6444,7 +6444,7 @@
       <c r="H58" s="30"/>
       <c r="I58" s="30"/>
     </row>
-    <row r="59" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="4:9">
       <c r="D59" s="30"/>
       <c r="E59" s="30"/>
       <c r="F59" s="30"/>
@@ -6452,7 +6452,7 @@
       <c r="H59" s="30"/>
       <c r="I59" s="30"/>
     </row>
-    <row r="60" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="4:9">
       <c r="D60" s="30"/>
       <c r="E60" s="30"/>
       <c r="F60" s="30"/>
@@ -6460,7 +6460,7 @@
       <c r="H60" s="30"/>
       <c r="I60" s="30"/>
     </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="4:9">
       <c r="D61" s="30"/>
       <c r="E61" s="30"/>
       <c r="F61" s="30"/>
@@ -6468,7 +6468,7 @@
       <c r="H61" s="30"/>
       <c r="I61" s="30"/>
     </row>
-    <row r="62" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="4:9">
       <c r="D62" s="30"/>
       <c r="E62" s="30"/>
       <c r="F62" s="30"/>
@@ -6476,7 +6476,7 @@
       <c r="H62" s="30"/>
       <c r="I62" s="30"/>
     </row>
-    <row r="63" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="4:9">
       <c r="D63" s="30"/>
       <c r="E63" s="30"/>
       <c r="F63" s="30"/>
@@ -6484,7 +6484,7 @@
       <c r="H63" s="30"/>
       <c r="I63" s="30"/>
     </row>
-    <row r="64" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="4:9">
       <c r="D64" s="30"/>
       <c r="E64" s="30"/>
       <c r="F64" s="30"/>
@@ -6492,7 +6492,7 @@
       <c r="H64" s="30"/>
       <c r="I64" s="30"/>
     </row>
-    <row r="65" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="4:9">
       <c r="D65" s="30"/>
       <c r="E65" s="30"/>
       <c r="F65" s="30"/>
@@ -6500,7 +6500,7 @@
       <c r="H65" s="30"/>
       <c r="I65" s="30"/>
     </row>
-    <row r="66" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="4:9">
       <c r="D66" s="30"/>
       <c r="E66" s="30"/>
       <c r="F66" s="30"/>
@@ -6508,7 +6508,7 @@
       <c r="H66" s="30"/>
       <c r="I66" s="30"/>
     </row>
-    <row r="67" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="4:9">
       <c r="D67" s="30"/>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
@@ -6516,7 +6516,7 @@
       <c r="H67" s="30"/>
       <c r="I67" s="30"/>
     </row>
-    <row r="68" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="4:9">
       <c r="D68" s="30"/>
       <c r="E68" s="30"/>
       <c r="F68" s="30"/>
@@ -6524,7 +6524,7 @@
       <c r="H68" s="30"/>
       <c r="I68" s="30"/>
     </row>
-    <row r="69" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="4:9">
       <c r="D69" s="30"/>
       <c r="E69" s="30"/>
       <c r="F69" s="30"/>
@@ -6532,7 +6532,7 @@
       <c r="H69" s="30"/>
       <c r="I69" s="30"/>
     </row>
-    <row r="70" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="4:9">
       <c r="D70" s="30"/>
       <c r="E70" s="30"/>
       <c r="F70" s="30"/>
@@ -6540,7 +6540,7 @@
       <c r="H70" s="30"/>
       <c r="I70" s="30"/>
     </row>
-    <row r="71" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="4:9">
       <c r="D71" s="30"/>
       <c r="E71" s="30"/>
       <c r="F71" s="30"/>
@@ -6548,7 +6548,7 @@
       <c r="H71" s="30"/>
       <c r="I71" s="30"/>
     </row>
-    <row r="72" spans="4:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="4:9">
       <c r="D72" s="30"/>
       <c r="E72" s="30"/>
       <c r="F72" s="30"/>
@@ -6569,7 +6569,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEBB537-D2E1-4D20-A494-C05A81D52093}">
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="15.58203125" style="11" customWidth="1"/>
@@ -6590,31 +6590,31 @@
     <col min="63" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.45">
-      <c r="B2" s="58" t="s">
+    <row r="2" spans="1:26">
+      <c r="B2" s="60" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.45">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4" s="57" t="s">
         <v>176</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:26">
       <c r="A5" s="57" t="s">
         <v>178</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:26">
       <c r="A6" s="57" t="s">
         <v>179</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="7" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:26" s="23" customFormat="1">
       <c r="A7" s="57"/>
       <c r="B7" s="1" t="s">
         <v>318</v>
@@ -6922,7 +6922,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:26" s="23" customFormat="1">
       <c r="A8" s="57"/>
       <c r="B8" s="1" t="s">
         <v>319</v>
@@ -7006,7 +7006,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:26" s="23" customFormat="1">
       <c r="A9" s="57"/>
       <c r="B9" s="1" t="s">
         <v>320</v>
@@ -7070,7 +7070,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="10" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:26" s="23" customFormat="1">
       <c r="A10" s="57"/>
       <c r="B10" s="1" t="s">
         <v>322</v>
@@ -7136,7 +7136,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="11" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:26" s="23" customFormat="1">
       <c r="A11" s="57"/>
       <c r="B11" s="1" t="s">
         <v>324</v>
@@ -7220,7 +7220,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:26" s="23" customFormat="1">
       <c r="A12" s="57"/>
       <c r="B12" s="1" t="s">
         <v>326</v>
@@ -7306,7 +7306,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:26" s="23" customFormat="1">
       <c r="A13" s="57"/>
       <c r="B13" s="1" t="s">
         <v>328</v>
@@ -7372,7 +7372,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="14" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:26" s="23" customFormat="1">
       <c r="A14" s="57"/>
       <c r="B14" s="1" t="s">
         <v>344</v>
@@ -7436,7 +7436,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:26" s="23" customFormat="1">
       <c r="A15" s="57"/>
       <c r="B15" s="1" t="s">
         <v>345</v>
@@ -7520,7 +7520,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:26" s="23" customFormat="1">
       <c r="A16" s="57"/>
       <c r="B16" s="1" t="s">
         <v>346</v>
@@ -7588,7 +7588,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:26" s="23" customFormat="1">
       <c r="A17" s="57"/>
       <c r="B17" s="1" t="s">
         <v>347</v>
@@ -7666,7 +7666,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="18" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:26" s="23" customFormat="1">
       <c r="A18" s="57"/>
       <c r="B18" s="1" t="s">
         <v>348</v>
@@ -7732,7 +7732,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="19" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:26" s="23" customFormat="1">
       <c r="A19" s="57"/>
       <c r="B19" s="1" t="s">
         <v>349</v>
@@ -7818,7 +7818,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="20" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:26" s="23" customFormat="1">
       <c r="A20" s="57"/>
       <c r="B20" s="1" t="s">
         <v>351</v>
@@ -7886,7 +7886,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="21" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:26" s="23" customFormat="1">
       <c r="A21" s="57"/>
       <c r="B21" s="1" t="s">
         <v>353</v>
@@ -7966,7 +7966,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="22" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:26" s="23" customFormat="1">
       <c r="A22" s="57"/>
       <c r="B22" s="1" t="s">
         <v>367</v>
@@ -8030,7 +8030,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="23" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:26" s="23" customFormat="1">
       <c r="A23" s="57"/>
       <c r="B23" s="1" t="s">
         <v>369</v>
@@ -8108,7 +8108,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="24" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:26" s="23" customFormat="1">
       <c r="A24" s="57"/>
       <c r="B24" s="1" t="s">
         <v>371</v>
@@ -8190,7 +8190,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:26" s="23" customFormat="1">
       <c r="A25" s="57"/>
       <c r="B25" s="1" t="s">
         <v>373</v>
@@ -8268,7 +8268,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="26" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:26" s="23" customFormat="1">
       <c r="A26" s="57"/>
       <c r="B26" s="1" t="s">
         <v>375</v>
@@ -8334,7 +8334,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="27" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:26" s="23" customFormat="1">
       <c r="A27" s="57"/>
       <c r="B27" s="1" t="s">
         <v>377</v>
@@ -8414,7 +8414,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="28" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:26" s="23" customFormat="1">
       <c r="A28" s="57"/>
       <c r="B28" s="1" t="s">
         <v>379</v>
@@ -8498,7 +8498,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="29" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:26" s="23" customFormat="1">
       <c r="A29" s="57"/>
       <c r="B29" s="1" t="s">
         <v>381</v>
@@ -8578,7 +8578,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="30" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:26" s="23" customFormat="1">
       <c r="A30" s="57"/>
       <c r="B30" s="1" t="s">
         <v>395</v>
@@ -8642,7 +8642,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="31" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:26" s="23" customFormat="1">
       <c r="A31" s="57"/>
       <c r="B31" s="1" t="s">
         <v>397</v>
@@ -8706,7 +8706,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="32" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:26" s="23" customFormat="1">
       <c r="A32" s="57"/>
       <c r="B32" s="1" t="s">
         <v>399</v>
@@ -8790,7 +8790,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" spans="1:26" s="23" customFormat="1" ht="34" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:26" s="23" customFormat="1" ht="34">
       <c r="A33" s="57"/>
       <c r="B33" s="1" t="s">
         <v>401</v>
@@ -8868,7 +8868,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="34" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:26" s="23" customFormat="1">
       <c r="A34" s="57"/>
       <c r="B34" s="1" t="s">
         <v>403</v>
@@ -8934,7 +8934,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="35" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:26" s="23" customFormat="1">
       <c r="A35" s="57"/>
       <c r="B35" s="1" t="s">
         <v>405</v>
@@ -9000,7 +9000,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="36" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:26" s="23" customFormat="1">
       <c r="A36" s="57"/>
       <c r="B36" s="1" t="s">
         <v>407</v>
@@ -9086,7 +9086,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="37" spans="1:26" s="23" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:26" s="23" customFormat="1">
       <c r="A37" s="57"/>
       <c r="B37" s="1" t="s">
         <v>409</v>
@@ -9166,7 +9166,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:26">
       <c r="A39" s="11" t="s">
         <v>180</v>
       </c>
@@ -9246,7 +9246,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:26">
       <c r="A40" s="11" t="s">
         <v>175</v>
       </c>
@@ -9264,7 +9264,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047AFDEF-8474-49A1-AB6C-5E66602F6994}">
   <dimension ref="A1:AR13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="10.5" style="11" customWidth="1"/>
     <col min="2" max="3" width="20.58203125" style="11" customWidth="1"/>
@@ -9291,36 +9291,36 @@
     <col min="45" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:44">
       <c r="A1" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B2" s="58" t="s">
+    <row r="2" spans="1:44">
+      <c r="B2" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+    </row>
+    <row r="4" spans="1:44">
       <c r="A4" s="11" t="s">
         <v>176</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>18</v>
       </c>
       <c r="X4" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y4" s="10" t="s">
         <v>19</v>
@@ -9454,7 +9454,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:44" ht="34" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:44" ht="34">
       <c r="A5" s="11" t="s">
         <v>178</v>
       </c>
@@ -9588,7 +9588,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="6" spans="1:44" ht="51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:44" ht="51">
       <c r="A6" s="11" t="s">
         <v>179</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:44" ht="34" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:44" ht="34">
       <c r="B7" s="13" t="s">
         <v>294</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:44" ht="51" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:44" ht="51">
       <c r="B8" s="13" t="s">
         <v>295</v>
       </c>
@@ -9888,7 +9888,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:44" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:44" ht="34">
       <c r="B9" s="13" t="s">
         <v>296</v>
       </c>
@@ -9987,7 +9987,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:44" ht="34" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:44" ht="34">
       <c r="B10" s="13" t="s">
         <v>297</v>
       </c>
@@ -10086,12 +10086,12 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:44">
       <c r="A12" s="11" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="13" spans="1:44" ht="102" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:44" ht="102">
       <c r="A13" s="11" t="s">
         <v>175</v>
       </c>
